--- a/docs/custos-nuvem.xlsx
+++ b/docs/custos-nuvem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilherme.portilho\Music\Codigos\GitHub\PI-2026.2\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA9CE8C-BE4F-4F79-BD97-8571F4B7C6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8006F705-AABE-42F2-A963-C775CB13EBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17700" yWindow="15735" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,58 +34,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="4">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="4">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1428,7 +1376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1437,19 +1385,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1484,54 +1419,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1549,34 +1447,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1603,7 +1480,7 @@
     <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1628,18 +1505,9 @@
     <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1648,9 +1516,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1674,57 +1539,137 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2275,88 +2220,185 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-    <v>Picture</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-    <v>Picture</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-    <v>Picture</v>
-  </rv>
-  <rv s="0">
-    <v>3</v>
-    <v>5</v>
-    <v>Picture</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="Text" t="s"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
-  <rel r:id="rId4"/>
-</richValueRels>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29934</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>25854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1686434</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>168461</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99081A0A-C98D-0D06-CFC1-9069969EA3A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6887934" y="5531304"/>
+          <a:ext cx="6800000" cy="4314557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>31296</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>31296</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1687796</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>173903</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94943CC0-C8B2-81C4-3950-8B7AEE01AAF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31296" y="5536746"/>
+          <a:ext cx="6800000" cy="4314557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1685075</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>171182</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6886283-FD01-CAB9-DD30-E2EA0E8187BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6886575" y="790575"/>
+          <a:ext cx="6800000" cy="4314557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>31296</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1687796</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>171182</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE031E0E-950F-665E-90B0-A72D57AA0B0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31296" y="790575"/>
+          <a:ext cx="6800000" cy="4314557"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2660,800 +2702,823 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="106">
         <v>5.5</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="107"/>
+      <c r="D5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="36" t="s">
+      <c r="G5" s="104"/>
+      <c r="H5" s="105" t="s">
         <v>285</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="28"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="28"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="28"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="28"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="21"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
     </row>
     <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="49" t="s">
+      <c r="E12" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="49" t="s">
+      <c r="G12" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="49" t="s">
+      <c r="I12" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="61" t="s">
+      <c r="J12" s="35" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="69">
+      <c r="C13" s="38">
         <f>'AWS - Detalhamento'!G6</f>
         <v>9.99</v>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="39">
         <f t="shared" ref="D13:D18" si="0">C13*$B$5</f>
         <v>54.945</v>
       </c>
-      <c r="E13" s="69">
+      <c r="E13" s="38">
         <f>'Azure - Detalhamento'!G6</f>
         <v>9.99</v>
       </c>
-      <c r="F13" s="70">
+      <c r="F13" s="39">
         <f t="shared" ref="F13:F18" si="1">E13*$B$5</f>
         <v>54.945</v>
       </c>
-      <c r="G13" s="69">
+      <c r="G13" s="38">
         <f>'GCP - Detalhamento'!G6</f>
         <v>9.11</v>
       </c>
-      <c r="H13" s="70">
+      <c r="H13" s="39">
         <f t="shared" ref="H13:H18" si="2">G13*$B$5</f>
         <v>50.104999999999997</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="10">
         <f t="shared" ref="I13:I18" si="3">AVERAGE(C13,E13,G13)</f>
         <v>9.6966666666666672</v>
       </c>
-      <c r="J13" s="68" t="s">
+      <c r="J13" s="37" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="72">
+      <c r="C14" s="41">
         <f>'AWS - Detalhamento'!G11</f>
         <v>0.05</v>
       </c>
-      <c r="D14" s="73">
+      <c r="D14" s="42">
         <f t="shared" si="0"/>
         <v>0.27500000000000002</v>
       </c>
-      <c r="E14" s="72">
+      <c r="E14" s="41">
         <f>'Azure - Detalhamento'!G11</f>
         <v>0.06</v>
       </c>
-      <c r="F14" s="73">
+      <c r="F14" s="42">
         <f t="shared" si="1"/>
         <v>0.32999999999999996</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="41">
         <f>'GCP - Detalhamento'!G11</f>
         <v>0.04</v>
       </c>
-      <c r="H14" s="73">
+      <c r="H14" s="42">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="13">
         <f t="shared" si="3"/>
         <v>4.9999999999999996E-2</v>
       </c>
-      <c r="J14" s="71" t="s">
+      <c r="J14" s="40" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="69">
+      <c r="C15" s="38">
         <f>'AWS - Detalhamento'!G14</f>
         <v>1</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="39">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="E15" s="69">
+      <c r="E15" s="38">
         <f>'Azure - Detalhamento'!G14</f>
         <v>0</v>
       </c>
-      <c r="F15" s="70">
+      <c r="F15" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="38">
         <f>'GCP - Detalhamento'!G14</f>
         <v>2.5</v>
       </c>
-      <c r="H15" s="70">
+      <c r="H15" s="39">
         <f t="shared" si="2"/>
         <v>13.75</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="10">
         <f t="shared" si="3"/>
         <v>1.1666666666666667</v>
       </c>
-      <c r="J15" s="68" t="s">
+      <c r="J15" s="37" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="41">
         <f>'AWS - Detalhamento'!G19</f>
         <v>2.8</v>
       </c>
-      <c r="D16" s="73">
+      <c r="D16" s="42">
         <f t="shared" si="0"/>
         <v>15.399999999999999</v>
       </c>
-      <c r="E16" s="72">
+      <c r="E16" s="41">
         <f>'Azure - Detalhamento'!G19</f>
         <v>1.5</v>
       </c>
-      <c r="F16" s="73">
+      <c r="F16" s="42">
         <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
-      <c r="G16" s="72">
+      <c r="G16" s="41">
         <f>'GCP - Detalhamento'!G19</f>
         <v>0</v>
       </c>
-      <c r="H16" s="73">
+      <c r="H16" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="13">
         <f t="shared" si="3"/>
         <v>1.4333333333333333</v>
       </c>
-      <c r="J16" s="71" t="s">
+      <c r="J16" s="40" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="69">
+      <c r="C17" s="38">
         <f>'AWS - Detalhamento'!G22</f>
         <v>0</v>
       </c>
-      <c r="D17" s="70">
+      <c r="D17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="69">
+      <c r="E17" s="38">
         <f>'Azure - Detalhamento'!G22</f>
         <v>0</v>
       </c>
-      <c r="F17" s="70">
+      <c r="F17" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="38">
         <f>'GCP - Detalhamento'!G22</f>
         <v>0</v>
       </c>
-      <c r="H17" s="70">
+      <c r="H17" s="39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="10">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="68" t="s">
+      <c r="J17" s="37" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="30">
         <f>SUM(C13:C17)</f>
         <v>13.84</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="31">
         <f t="shared" si="0"/>
         <v>76.12</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="30">
         <f>SUM(E13:E17)</f>
         <v>11.55</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="31">
         <f t="shared" si="1"/>
         <v>63.525000000000006</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="30">
         <f>SUM(G13:G17)</f>
         <v>11.649999999999999</v>
       </c>
-      <c r="H18" s="53">
+      <c r="H18" s="31">
         <f t="shared" si="2"/>
         <v>64.074999999999989</v>
       </c>
-      <c r="I18" s="52">
+      <c r="I18" s="30">
         <f t="shared" si="3"/>
         <v>12.346666666666666</v>
       </c>
-      <c r="J18" s="54" t="s">
+      <c r="J18" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="16">
         <f t="shared" ref="C19:I19" si="4">C18*12</f>
         <v>166.07999999999998</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="17">
         <f t="shared" si="4"/>
         <v>913.44</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="16">
         <f t="shared" si="4"/>
         <v>138.60000000000002</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="17">
         <f t="shared" si="4"/>
         <v>762.30000000000007</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="16">
         <f t="shared" si="4"/>
         <v>139.79999999999998</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="17">
         <f t="shared" si="4"/>
         <v>768.89999999999986</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="16">
         <f t="shared" si="4"/>
         <v>148.16</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="127"/>
-      <c r="C22" s="127"/>
-      <c r="D22" s="127"/>
-      <c r="E22" s="127"/>
-      <c r="F22" s="127"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="127"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
     </row>
     <row r="23" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="49" t="s">
+      <c r="E23" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="49" t="s">
+      <c r="F23" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="49" t="s">
+      <c r="G23" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="49" t="s">
+      <c r="H23" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="65" t="s">
+      <c r="I23" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J23" s="61" t="s">
+      <c r="J23" s="35" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="13">
         <f t="shared" ref="C24:H24" si="5">C18</f>
         <v>13.84</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="12">
         <f t="shared" si="5"/>
         <v>76.12</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="13">
         <f t="shared" si="5"/>
         <v>11.55</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="12">
         <f t="shared" si="5"/>
         <v>63.525000000000006</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="13">
         <f t="shared" si="5"/>
         <v>11.649999999999999</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="12">
         <f t="shared" si="5"/>
         <v>64.074999999999989</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="19">
         <f>(E24-C24)/C24</f>
         <v>-0.16546242774566469</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="19">
         <f>(G24-C24)/C24</f>
         <v>-0.15823699421965326</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="10">
         <f>'AWS - Detalhamento'!G29</f>
         <v>11.040000000000001</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="9">
         <f>C25*$B$5</f>
         <v>60.720000000000006</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="10">
         <f>'Azure - Detalhamento'!G29</f>
         <v>10.050000000000001</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="9">
         <f>E25*$B$5</f>
         <v>55.275000000000006</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="10">
         <f>'GCP - Detalhamento'!G29</f>
         <v>11.649999999999999</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="9">
         <f>G25*$B$5</f>
         <v>64.074999999999989</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="20">
         <f>(E25-C25)/C25</f>
         <v>-8.9673913043478271E-2</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="20">
         <f>(G25-C25)/C25</f>
         <v>5.5253623188405578E-2</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="66" t="s">
+      <c r="B26" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="13">
         <f>'AWS - Detalhamento'!G26</f>
         <v>23.83</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="12">
         <f>C26*$B$5</f>
         <v>131.065</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="13">
         <f>'Azure - Detalhamento'!G26</f>
         <v>21.54</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="12">
         <f>E26*$B$5</f>
         <v>118.47</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="13">
         <f>'GCP - Detalhamento'!G26</f>
         <v>20.759999999999998</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="12">
         <f>G26*$B$5</f>
         <v>114.17999999999999</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="19">
         <f>(E26-C26)/C26</f>
         <v>-9.6097356273604675E-2</v>
       </c>
-      <c r="J26" s="26">
+      <c r="J26" s="19">
         <f>(G26-C26)/C26</f>
         <v>-0.12882920688208144</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
     </row>
     <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="126" t="s">
+      <c r="A29" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="127"/>
-      <c r="C29" s="127"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="112"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="112"/>
+      <c r="H29" s="112"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="112"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="62" t="s">
+      <c r="A30" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="63"/>
-      <c r="C30" s="64" t="s">
+      <c r="B30" s="114"/>
+      <c r="C30" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="63"/>
-      <c r="E30" s="64" t="s">
+      <c r="D30" s="114"/>
+      <c r="E30" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="63"/>
-      <c r="G30" s="64" t="s">
+      <c r="F30" s="114"/>
+      <c r="G30" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="63"/>
-      <c r="I30" s="64" t="s">
+      <c r="H30" s="114"/>
+      <c r="I30" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="J30" s="63"/>
+      <c r="J30" s="114"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="99" t="s">
         <v>286</v>
       </c>
-      <c r="B31" s="58"/>
-      <c r="C31" s="55" t="s">
+      <c r="B31" s="100"/>
+      <c r="C31" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="56"/>
-      <c r="E31" s="55" t="s">
+      <c r="D31" s="97"/>
+      <c r="E31" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="56"/>
-      <c r="G31" s="55" t="s">
+      <c r="F31" s="97"/>
+      <c r="G31" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="H31" s="56"/>
-      <c r="I31" s="13" t="s">
+      <c r="H31" s="97"/>
+      <c r="I31" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="J31" s="12"/>
+      <c r="J31" s="97"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="60" t="s">
+      <c r="A32" s="101" t="s">
         <v>287</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="57" t="s">
+      <c r="B32" s="100"/>
+      <c r="C32" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="56"/>
-      <c r="E32" s="57" t="s">
+      <c r="D32" s="97"/>
+      <c r="E32" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="56"/>
-      <c r="G32" s="57" t="s">
+      <c r="F32" s="97"/>
+      <c r="G32" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="H32" s="56"/>
-      <c r="I32" s="14" t="s">
+      <c r="H32" s="97"/>
+      <c r="I32" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="J32" s="12"/>
+      <c r="J32" s="97"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="59" t="s">
+      <c r="A33" s="99" t="s">
         <v>288</v>
       </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="55" t="s">
+      <c r="B33" s="100"/>
+      <c r="C33" s="96" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="55" t="s">
+      <c r="D33" s="97"/>
+      <c r="E33" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="56"/>
-      <c r="G33" s="55" t="s">
+      <c r="F33" s="97"/>
+      <c r="G33" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="H33" s="56"/>
-      <c r="I33" s="13" t="s">
+      <c r="H33" s="97"/>
+      <c r="I33" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="J33" s="12"/>
+      <c r="J33" s="97"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="101" t="s">
         <v>289</v>
       </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="57" t="s">
+      <c r="B34" s="100"/>
+      <c r="C34" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="57" t="s">
+      <c r="D34" s="97"/>
+      <c r="E34" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="56"/>
-      <c r="G34" s="57" t="s">
+      <c r="F34" s="97"/>
+      <c r="G34" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="H34" s="56"/>
-      <c r="I34" s="14" t="s">
+      <c r="H34" s="97"/>
+      <c r="I34" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="J34" s="12"/>
+      <c r="J34" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="I31:J31"/>
@@ -3470,29 +3535,6 @@
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="H7:I8"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -3516,68 +3558,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-    </row>
-    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="D5" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="88" t="s">
+      <c r="E5" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="88" t="s">
+      <c r="G5" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="88" t="s">
+      <c r="H5" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="88" t="s">
+      <c r="I5" s="57" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3585,480 +3627,476 @@
       <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="79">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48">
         <f>SUM(G7:G8)</f>
         <v>9.99</v>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="49">
         <f>G6*'Resumo Comparativo'!$B$5</f>
         <v>54.945</v>
       </c>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="50" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="44" t="s">
         <v>83</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="75" t="s">
+      <c r="E7" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="52">
         <v>7.59</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="53">
         <f>G7*'Resumo Comparativo'!$B$5</f>
         <v>41.744999999999997</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="43" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="46" t="s">
         <v>89</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="86">
+      <c r="G8" s="55">
         <v>2.4</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="56">
         <f>G8*'Resumo Comparativo'!$B$5</f>
         <v>13.2</v>
       </c>
-      <c r="I8" s="76" t="s">
+      <c r="I8" s="45" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
       <c r="B9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79">
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48">
         <f>SUM(G12:G13)</f>
         <v>13.14</v>
       </c>
-      <c r="H9" s="80">
+      <c r="H9" s="49">
         <f>G9*'Resumo Comparativo'!$B$5</f>
         <v>72.27000000000001</v>
       </c>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="50" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="46" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="55">
         <v>0.23</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="56">
         <f>G10*'Resumo Comparativo'!$B$5</f>
         <v>1.2650000000000001</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="45" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="44" t="s">
         <v>105</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="52">
         <v>0.05</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="53">
         <f>G11*'Resumo Comparativo'!$B$5</f>
         <v>0.27500000000000002</v>
       </c>
-      <c r="I11" s="74" t="s">
+      <c r="I11" s="43" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
       <c r="B12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79">
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48">
         <f>SUM(G15:G16)</f>
         <v>13.14</v>
       </c>
-      <c r="H12" s="80">
+      <c r="H12" s="49">
         <f>G12*'Resumo Comparativo'!$B$5</f>
         <v>72.27000000000001</v>
       </c>
-      <c r="I12" s="81" t="s">
+      <c r="I12" s="50" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="44" t="s">
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="52">
         <v>0</v>
       </c>
-      <c r="H13" s="84">
+      <c r="H13" s="53">
         <f>G13*'Resumo Comparativo'!$B$5</f>
         <v>0</v>
       </c>
-      <c r="I13" s="74" t="s">
+      <c r="I13" s="43" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="46" t="s">
         <v>121</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="55">
         <v>1</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="56">
         <f>G14*'Resumo Comparativo'!$B$5</f>
         <v>5.5</v>
       </c>
-      <c r="I14" s="76" t="s">
+      <c r="I14" s="45" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="107"/>
       <c r="B15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79">
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48">
         <f>SUM(G20:G21)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="49">
         <f>G15*'Resumo Comparativo'!$B$5</f>
         <v>0</v>
       </c>
-      <c r="I15" s="81" t="s">
+      <c r="I15" s="50" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="46" t="s">
         <v>130</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="55">
         <v>13.14</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="56">
         <f>G16*'Resumo Comparativo'!$B$5</f>
         <v>72.27000000000001</v>
       </c>
-      <c r="I16" s="76" t="s">
+      <c r="I16" s="45" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="44" t="s">
         <v>135</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="52">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H17" s="84">
+      <c r="H17" s="53">
         <f>G17*'Resumo Comparativo'!$B$5</f>
         <v>12.649999999999999</v>
       </c>
-      <c r="I17" s="74" t="s">
+      <c r="I17" s="43" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="107"/>
       <c r="B18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="79">
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48">
         <f>G23</f>
         <v>13.84</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="49">
         <f>G18*'Resumo Comparativo'!$B$5</f>
         <v>76.12</v>
       </c>
-      <c r="I18" s="81" t="s">
+      <c r="I18" s="50" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="44" t="s">
         <v>144</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="52">
         <v>2.8</v>
       </c>
-      <c r="H19" s="84">
+      <c r="H19" s="53">
         <f>G19*'Resumo Comparativo'!$B$5</f>
         <v>15.399999999999999</v>
       </c>
-      <c r="I19" s="74" t="s">
+      <c r="I19" s="43" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
     </row>
     <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="93">
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="59">
         <f>G6+G11+G14+G19+G22</f>
         <v>13.84</v>
       </c>
-      <c r="H23" s="94">
+      <c r="H23" s="60">
         <f>G23*'Resumo Comparativo'!$B$5</f>
         <v>76.12</v>
       </c>
-      <c r="I23" s="95" t="s">
+      <c r="I23" s="61" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="28" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="115"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="120"/>
+    <row r="24" spans="1:9" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="79"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="96" t="s">
+      <c r="A25" s="119" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="71" t="s">
         <v>154</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="E26" s="106" t="s">
+      <c r="E26" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="98">
+      <c r="G26" s="63">
         <f>G23+9.99</f>
         <v>23.83</v>
       </c>
-      <c r="H26" s="99">
+      <c r="H26" s="64">
         <f>G26*'Resumo Comparativo'!$B$5</f>
         <v>131.065</v>
       </c>
@@ -4066,54 +4104,54 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="114"/>
+    <row r="27" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="72"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="78"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="119" t="s">
         <v>160</v>
       </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="94"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="103" t="s">
+      <c r="A29" s="68" t="s">
         <v>161</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="66" t="s">
         <v>163</v>
       </c>
-      <c r="D29" s="102" t="s">
+      <c r="D29" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="E29" s="103" t="s">
+      <c r="E29" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="103" t="s">
+      <c r="F29" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="G29" s="97">
+      <c r="G29" s="62">
         <f>G6+G11+G14+G22+0</f>
         <v>11.040000000000001</v>
       </c>
-      <c r="H29" s="100">
+      <c r="H29" s="65">
         <f>G29*'Resumo Comparativo'!$B$5</f>
         <v>60.720000000000006</v>
       </c>
@@ -4150,68 +4188,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="120" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="123" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-    </row>
-    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="D5" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="88" t="s">
+      <c r="E5" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="88" t="s">
+      <c r="G5" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="88" t="s">
+      <c r="H5" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="88" t="s">
+      <c r="I5" s="57" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4219,447 +4257,443 @@
       <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="79">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48">
         <f>SUM(G7:G8)</f>
         <v>9.99</v>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="49">
         <f>G6*'Resumo Comparativo'!$B$5</f>
         <v>54.945</v>
       </c>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="50" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="44" t="s">
         <v>170</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="E7" s="75" t="s">
+      <c r="E7" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="52">
         <v>7.59</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="53">
         <f>G7*'Resumo Comparativo'!$B$5</f>
         <v>41.744999999999997</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="43" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="46" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="86">
+      <c r="G8" s="55">
         <v>2.4</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="56">
         <f>G8*'Resumo Comparativo'!$B$5</f>
         <v>13.2</v>
       </c>
-      <c r="I8" s="76" t="s">
+      <c r="I8" s="45" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
       <c r="B9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79">
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48">
         <f>SUM(G12:G13)</f>
         <v>21.1</v>
       </c>
-      <c r="H9" s="80">
+      <c r="H9" s="49">
         <f>G9*'Resumo Comparativo'!$B$5</f>
         <v>116.05000000000001</v>
       </c>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="50" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="46" t="s">
         <v>180</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="55">
         <v>0.18</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="56">
         <f>G10*'Resumo Comparativo'!$B$5</f>
         <v>0.99</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="45" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="44" t="s">
         <v>184</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="52">
         <v>0.06</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="53">
         <f>G11*'Resumo Comparativo'!$B$5</f>
         <v>0.32999999999999996</v>
       </c>
-      <c r="I11" s="74" t="s">
+      <c r="I11" s="43" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
       <c r="B12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79">
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48">
         <f>SUM(G15:G16)</f>
         <v>13</v>
       </c>
-      <c r="H12" s="80">
+      <c r="H12" s="49">
         <f>G12*'Resumo Comparativo'!$B$5</f>
         <v>71.5</v>
       </c>
-      <c r="I12" s="81" t="s">
+      <c r="I12" s="50" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="44" t="s">
         <v>190</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="52">
         <v>8.1</v>
       </c>
-      <c r="H13" s="84">
+      <c r="H13" s="53">
         <f>G13*'Resumo Comparativo'!$B$5</f>
         <v>44.55</v>
       </c>
-      <c r="I13" s="74" t="s">
+      <c r="I13" s="43" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="46" t="s">
         <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="54" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="55">
         <v>0</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="56">
         <f>G14*'Resumo Comparativo'!$B$5</f>
         <v>0</v>
       </c>
-      <c r="I14" s="76" t="s">
+      <c r="I14" s="45" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="107"/>
       <c r="B15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79">
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48">
         <f>SUM(G20:G21)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="49">
         <f>G15*'Resumo Comparativo'!$B$5</f>
         <v>0</v>
       </c>
-      <c r="I15" s="81" t="s">
+      <c r="I15" s="50" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="46" t="s">
         <v>202</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="55">
         <v>13</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="56">
         <f>G16*'Resumo Comparativo'!$B$5</f>
         <v>71.5</v>
       </c>
-      <c r="I16" s="76" t="s">
+      <c r="I16" s="45" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="44" t="s">
         <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="51" t="s">
         <v>207</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="52">
         <v>3.68</v>
       </c>
-      <c r="H17" s="84">
+      <c r="H17" s="53">
         <f>G17*'Resumo Comparativo'!$B$5</f>
         <v>20.240000000000002</v>
       </c>
-      <c r="I17" s="74" t="s">
+      <c r="I17" s="43" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="107"/>
       <c r="B18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="79">
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48">
         <f>G23</f>
         <v>11.55</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="49">
         <f>G18*'Resumo Comparativo'!$B$5</f>
         <v>63.525000000000006</v>
       </c>
-      <c r="I18" s="81" t="s">
+      <c r="I18" s="50" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="44" t="s">
         <v>211</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="52">
         <v>1.5</v>
       </c>
-      <c r="H19" s="84">
+      <c r="H19" s="53">
         <f>G19*'Resumo Comparativo'!$B$5</f>
         <v>8.25</v>
       </c>
-      <c r="I19" s="74" t="s">
+      <c r="I19" s="43" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="93">
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="59">
         <f>G6+G11+G14+G19+G22</f>
         <v>11.55</v>
       </c>
-      <c r="H23" s="94">
+      <c r="H23" s="60">
         <f>G23*'Resumo Comparativo'!$B$5</f>
         <v>63.525000000000006</v>
       </c>
-      <c r="I23" s="95" t="s">
+      <c r="I23" s="61" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="115"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="120"/>
+      <c r="A24" s="79"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="96" t="s">
+      <c r="A25" s="119" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="71" t="s">
         <v>215</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="E26" s="106" t="s">
+      <c r="E26" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="98">
+      <c r="G26" s="63">
         <f>G23+9.99</f>
         <v>21.54</v>
       </c>
-      <c r="H26" s="99">
+      <c r="H26" s="64">
         <f>G26*'Resumo Comparativo'!$B$5</f>
         <v>118.47</v>
       </c>
@@ -4668,53 +4702,53 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="114"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="78"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="119" t="s">
         <v>160</v>
       </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="94"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="103" t="s">
+      <c r="A29" s="68" t="s">
         <v>219</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="66" t="s">
         <v>221</v>
       </c>
-      <c r="D29" s="102" t="s">
+      <c r="D29" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="103" t="s">
+      <c r="E29" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="103" t="s">
+      <c r="F29" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="G29" s="97">
+      <c r="G29" s="62">
         <f>G6+G11+G14+G22+0</f>
         <v>10.050000000000001</v>
       </c>
-      <c r="H29" s="100">
+      <c r="H29" s="65">
         <f>G29*'Resumo Comparativo'!$B$5</f>
         <v>55.275000000000006</v>
       </c>
@@ -4750,68 +4784,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="120" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="123" t="s">
         <v>225</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
     </row>
     <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="88" t="s">
+      <c r="C5" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="D5" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="88" t="s">
+      <c r="E5" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="88" t="s">
+      <c r="G5" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="88" t="s">
+      <c r="H5" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="I5" s="88" t="s">
+      <c r="I5" s="57" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4819,447 +4853,443 @@
       <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="79">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48">
         <f>SUM(G7:G8)</f>
         <v>9.11</v>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="49">
         <f>G6*'Resumo Comparativo'!$B$5</f>
         <v>50.104999999999997</v>
       </c>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="44" t="s">
         <v>227</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="43" t="s">
         <v>229</v>
       </c>
-      <c r="E7" s="75" t="s">
+      <c r="E7" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="52">
         <v>6.11</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="53">
         <f>G7*'Resumo Comparativo'!$B$5</f>
         <v>33.605000000000004</v>
       </c>
-      <c r="I7" s="74" t="s">
+      <c r="I7" s="43" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="46" t="s">
         <v>231</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="77" t="s">
+      <c r="F8" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="86">
+      <c r="G8" s="55">
         <v>3</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="56">
         <f>G8*'Resumo Comparativo'!$B$5</f>
         <v>16.5</v>
       </c>
-      <c r="I8" s="76" t="s">
+      <c r="I8" s="45" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
       <c r="B9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="79">
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48">
         <f>SUM(G12:G13)</f>
         <v>15.67</v>
       </c>
-      <c r="H9" s="80">
+      <c r="H9" s="49">
         <f>G9*'Resumo Comparativo'!$B$5</f>
         <v>86.185000000000002</v>
       </c>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="50" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="46" t="s">
         <v>236</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="55">
         <v>0.2</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="56">
         <f>G10*'Resumo Comparativo'!$B$5</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="45" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="44" t="s">
         <v>240</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="43" t="s">
         <v>242</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="52">
         <v>0.04</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="53">
         <f>G11*'Resumo Comparativo'!$B$5</f>
         <v>0.22</v>
       </c>
-      <c r="I11" s="74" t="s">
+      <c r="I11" s="43" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
       <c r="B12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79">
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48">
         <f>SUM(G15:G16)</f>
         <v>7.67</v>
       </c>
-      <c r="H12" s="80">
+      <c r="H12" s="49">
         <f>G12*'Resumo Comparativo'!$B$5</f>
         <v>42.185000000000002</v>
       </c>
-      <c r="I12" s="81" t="s">
+      <c r="I12" s="50" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="44" t="s">
         <v>245</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="43" t="s">
         <v>248</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="52">
         <v>8</v>
       </c>
-      <c r="H13" s="84">
+      <c r="H13" s="53">
         <f>G13*'Resumo Comparativo'!$B$5</f>
         <v>44</v>
       </c>
-      <c r="I13" s="74" t="s">
+      <c r="I13" s="43" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="s">
+      <c r="A14" s="46" t="s">
         <v>250</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="45" t="s">
         <v>253</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="55">
         <v>2.5</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="56">
         <f>G14*'Resumo Comparativo'!$B$5</f>
         <v>13.75</v>
       </c>
-      <c r="I14" s="76" t="s">
+      <c r="I14" s="45" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="107"/>
       <c r="B15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79">
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48">
         <f>SUM(G20:G21)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="49">
         <f>G15*'Resumo Comparativo'!$B$5</f>
         <v>0</v>
       </c>
-      <c r="I15" s="81" t="s">
+      <c r="I15" s="50" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="77" t="s">
+      <c r="A16" s="46" t="s">
         <v>257</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="45" t="s">
         <v>259</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="55">
         <v>7.67</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="56">
         <f>G16*'Resumo Comparativo'!$B$5</f>
         <v>42.185000000000002</v>
       </c>
-      <c r="I16" s="76" t="s">
+      <c r="I16" s="45" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="75" t="s">
+      <c r="A17" s="44" t="s">
         <v>261</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="F17" s="75" t="s">
+      <c r="F17" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="52">
         <v>5</v>
       </c>
-      <c r="H17" s="84">
+      <c r="H17" s="53">
         <f>G17*'Resumo Comparativo'!$B$5</f>
         <v>27.5</v>
       </c>
-      <c r="I17" s="74" t="s">
+      <c r="I17" s="43" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="107"/>
       <c r="B18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="79">
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48">
         <f>G23</f>
         <v>11.649999999999999</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="49">
         <f>G18*'Resumo Comparativo'!$B$5</f>
         <v>64.074999999999989</v>
       </c>
-      <c r="I18" s="81" t="s">
+      <c r="I18" s="50" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="75" t="s">
+      <c r="A19" s="44" t="s">
         <v>266</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="51" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="74" t="s">
+      <c r="D19" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="52">
         <v>0</v>
       </c>
-      <c r="H19" s="84">
+      <c r="H19" s="53">
         <f>G19*'Resumo Comparativo'!$B$5</f>
         <v>0</v>
       </c>
-      <c r="I19" s="74" t="s">
+      <c r="I19" s="43" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="58" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="121" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="93">
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="59">
         <f>G6+G11+G14+G19+G22</f>
         <v>11.649999999999999</v>
       </c>
-      <c r="H23" s="94">
+      <c r="H23" s="60">
         <f>G23*'Resumo Comparativo'!$B$5</f>
         <v>64.074999999999989</v>
       </c>
-      <c r="I23" s="95" t="s">
+      <c r="I23" s="61" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="115"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="119"/>
-      <c r="I24" s="120"/>
+      <c r="A24" s="79"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="84"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="96" t="s">
+      <c r="A25" s="119" t="s">
         <v>153</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="94"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="71" t="s">
         <v>270</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C26" s="104" t="s">
+      <c r="C26" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="D26" s="105" t="s">
+      <c r="D26" s="70" t="s">
         <v>272</v>
       </c>
-      <c r="E26" s="106" t="s">
+      <c r="E26" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="71" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="98">
+      <c r="G26" s="63">
         <f>G23+9.11</f>
         <v>20.759999999999998</v>
       </c>
-      <c r="H26" s="99">
+      <c r="H26" s="64">
         <f>G26*'Resumo Comparativo'!$B$5</f>
         <v>114.17999999999999</v>
       </c>
@@ -5268,53 +5298,53 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="114"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="78"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="119" t="s">
         <v>160</v>
       </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="94"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="103" t="s">
+      <c r="A29" s="68" t="s">
         <v>274</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="66" t="s">
         <v>276</v>
       </c>
-      <c r="D29" s="102" t="s">
+      <c r="D29" s="67" t="s">
         <v>277</v>
       </c>
-      <c r="E29" s="103" t="s">
+      <c r="E29" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="103" t="s">
+      <c r="F29" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="G29" s="97">
+      <c r="G29" s="62">
         <f>G6+G11+G14+G22+0</f>
         <v>11.649999999999999</v>
       </c>
-      <c r="H29" s="100">
+      <c r="H29" s="65">
         <f>G29*'Resumo Comparativo'!$B$5</f>
         <v>64.074999999999989</v>
       </c>
@@ -5343,547 +5373,541 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="86" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="93" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="123" t="s">
+      <c r="A4" s="95" t="s">
         <v>281</v>
       </c>
-      <c r="B4" s="123"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="10" t="s">
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="89" t="s">
         <v>282</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="124" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="124"/>
-      <c r="B6" s="124"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="124"/>
-      <c r="B7" s="124"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="124"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="124"/>
-      <c r="B9" s="124"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="124"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="124"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="124"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="124"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="124"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="124"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="124"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="88"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="88"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="88"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="124"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="88"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="124"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="124"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="124"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="124"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="124"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="124"/>
-      <c r="G21" s="124"/>
-      <c r="H21" s="124"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="88"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="124"/>
-      <c r="B22" s="124"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="124"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="124"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="124"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="124"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="124"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="124"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="124"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="124"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="124"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="124"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="124"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="125"/>
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="91" t="s">
         <v>283</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="9" t="s">
+      <c r="B29" s="90"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="92" t="s">
         <v>284</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="124" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="124"/>
-      <c r="D30" s="124"/>
-      <c r="E30" s="124" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F30" s="124"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="124"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="124"/>
-      <c r="B31" s="124"/>
-      <c r="C31" s="124"/>
-      <c r="D31" s="124"/>
-      <c r="E31" s="124"/>
-      <c r="F31" s="124"/>
-      <c r="G31" s="124"/>
-      <c r="H31" s="124"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="124"/>
-      <c r="B32" s="124"/>
-      <c r="C32" s="124"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="124"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="124"/>
-      <c r="B33" s="124"/>
-      <c r="C33" s="124"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="124"/>
+      <c r="A33" s="88"/>
+      <c r="B33" s="88"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="124"/>
-      <c r="B34" s="124"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="124"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="124"/>
+      <c r="A34" s="88"/>
+      <c r="B34" s="88"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="88"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="124"/>
-      <c r="B35" s="124"/>
-      <c r="C35" s="124"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="124"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="124"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="124"/>
-      <c r="B36" s="124"/>
-      <c r="C36" s="124"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="88"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="124"/>
-      <c r="B37" s="124"/>
-      <c r="C37" s="124"/>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="124"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="124"/>
-      <c r="B38" s="124"/>
-      <c r="C38" s="124"/>
-      <c r="D38" s="124"/>
-      <c r="E38" s="124"/>
-      <c r="F38" s="124"/>
-      <c r="G38" s="124"/>
-      <c r="H38" s="124"/>
+      <c r="A38" s="88"/>
+      <c r="B38" s="88"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="88"/>
+      <c r="H38" s="88"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="124"/>
-      <c r="B39" s="124"/>
-      <c r="C39" s="124"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="124"/>
-      <c r="G39" s="124"/>
-      <c r="H39" s="124"/>
+      <c r="A39" s="88"/>
+      <c r="B39" s="88"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
+      <c r="E39" s="88"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="88"/>
+      <c r="H39" s="88"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="124"/>
-      <c r="B40" s="124"/>
-      <c r="C40" s="124"/>
-      <c r="D40" s="124"/>
-      <c r="E40" s="124"/>
-      <c r="F40" s="124"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="124"/>
+      <c r="A40" s="88"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="88"/>
+      <c r="H40" s="88"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="124"/>
-      <c r="B41" s="124"/>
-      <c r="C41" s="124"/>
-      <c r="D41" s="124"/>
-      <c r="E41" s="124"/>
-      <c r="F41" s="124"/>
-      <c r="G41" s="124"/>
-      <c r="H41" s="124"/>
+      <c r="A41" s="88"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="124"/>
-      <c r="B42" s="124"/>
-      <c r="C42" s="124"/>
-      <c r="D42" s="124"/>
-      <c r="E42" s="124"/>
-      <c r="F42" s="124"/>
-      <c r="G42" s="124"/>
-      <c r="H42" s="124"/>
+      <c r="A42" s="88"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="88"/>
+      <c r="H42" s="88"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="124"/>
-      <c r="B43" s="124"/>
-      <c r="C43" s="124"/>
-      <c r="D43" s="124"/>
-      <c r="E43" s="124"/>
-      <c r="F43" s="124"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="124"/>
+      <c r="A43" s="88"/>
+      <c r="B43" s="88"/>
+      <c r="C43" s="88"/>
+      <c r="D43" s="88"/>
+      <c r="E43" s="88"/>
+      <c r="F43" s="88"/>
+      <c r="G43" s="88"/>
+      <c r="H43" s="88"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="124"/>
-      <c r="B44" s="124"/>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="124"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="124"/>
+      <c r="A44" s="88"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="88"/>
+      <c r="H44" s="88"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="124"/>
-      <c r="B45" s="124"/>
-      <c r="C45" s="124"/>
-      <c r="D45" s="124"/>
-      <c r="E45" s="124"/>
-      <c r="F45" s="124"/>
-      <c r="G45" s="124"/>
-      <c r="H45" s="124"/>
+      <c r="A45" s="88"/>
+      <c r="B45" s="88"/>
+      <c r="C45" s="88"/>
+      <c r="D45" s="88"/>
+      <c r="E45" s="88"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="88"/>
+      <c r="H45" s="88"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="124"/>
-      <c r="B46" s="124"/>
-      <c r="C46" s="124"/>
-      <c r="D46" s="124"/>
-      <c r="E46" s="124"/>
-      <c r="F46" s="124"/>
-      <c r="G46" s="124"/>
-      <c r="H46" s="124"/>
+      <c r="A46" s="88"/>
+      <c r="B46" s="88"/>
+      <c r="C46" s="88"/>
+      <c r="D46" s="88"/>
+      <c r="E46" s="88"/>
+      <c r="F46" s="88"/>
+      <c r="G46" s="88"/>
+      <c r="H46" s="88"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="124"/>
-      <c r="B47" s="124"/>
-      <c r="C47" s="124"/>
-      <c r="D47" s="124"/>
-      <c r="E47" s="124"/>
-      <c r="F47" s="124"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="124"/>
+      <c r="A47" s="88"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="88"/>
+      <c r="D47" s="88"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="88"/>
+      <c r="G47" s="88"/>
+      <c r="H47" s="88"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="124"/>
-      <c r="B48" s="124"/>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="88"/>
+      <c r="E48" s="88"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="88"/>
+      <c r="H48" s="88"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="124"/>
-      <c r="B49" s="124"/>
-      <c r="C49" s="124"/>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-      <c r="F49" s="124"/>
-      <c r="G49" s="124"/>
-      <c r="H49" s="124"/>
+      <c r="A49" s="88"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="88"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="88"/>
+      <c r="H49" s="88"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="124"/>
-      <c r="B50" s="124"/>
-      <c r="C50" s="124"/>
-      <c r="D50" s="124"/>
-      <c r="E50" s="124"/>
-      <c r="F50" s="124"/>
-      <c r="G50" s="124"/>
-      <c r="H50" s="124"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="88"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="88"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="88"/>
+      <c r="H50" s="88"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="124"/>
-      <c r="B51" s="124"/>
-      <c r="C51" s="124"/>
-      <c r="D51" s="124"/>
-      <c r="E51" s="124"/>
-      <c r="F51" s="124"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="124"/>
+      <c r="A51" s="88"/>
+      <c r="B51" s="88"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="88"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="124"/>
-      <c r="B52" s="124"/>
-      <c r="C52" s="124"/>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
+      <c r="A52" s="88"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="88"/>
+      <c r="D52" s="88"/>
+      <c r="E52" s="88"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="88"/>
+      <c r="H52" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A30:D52"/>
+    <mergeCell ref="E30:H52"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A5:D27"/>
     <mergeCell ref="E4:H4"/>
@@ -5892,9 +5916,8 @@
     <mergeCell ref="E29:H29"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A30:D52"/>
-    <mergeCell ref="E30:H52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>